--- a/output/pdf_financials_xlsx/UNC.xlsx
+++ b/output/pdf_financials_xlsx/UNC.xlsx
@@ -5922,40 +5922,40 @@
         </is>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.507091</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.274666</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.310254</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.260912</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.346723</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.9977780000000001</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.473795</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>1.908925</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>1.204794</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>729.226</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>1152.804</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>1031.238</v>
       </c>
     </row>
     <row r="116">
@@ -6252,22 +6252,22 @@
         <v>0</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-0.005601</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0</v>
+        <v>-0.002516</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-0.00184</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-52.183</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-40.532</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-0.697</v>
       </c>
     </row>
     <row r="122">
@@ -9365,7 +9365,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -9881,7 +9885,11 @@
           <t>Repurchase of Common Shares</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -10520,7 +10528,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
